--- a/casino-finance-model-v2.xlsx
+++ b/casino-finance-model-v2.xlsx
@@ -15,6 +15,7 @@
     <sheet name="ダッシュボード" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="取得時間" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="収入設計" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="定員プラン" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -166,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -208,10 +209,27 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F8696B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -725,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F92"/>
+  <dimension ref="A1:F94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1026,7 +1044,7 @@
         <v>0</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E16" s="13">
         <f>C16*D16</f>
@@ -1034,7 +1052,7 @@
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>完全歩合制=基本給0。全収入は面接歩合(上限12万)</t>
+          <t>完全歩合(基本給0)。理想6人=統括1+従者3-5+見習0-2・各上限12万</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1640,7 @@
         <v>5000</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E42" s="13">
         <f>C42*D42</f>
@@ -1630,7 +1648,7 @@
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>継続/レベルで逓増。支給額×件数</t>
+          <t>刻:30日5万/100日10万/200日15万/300日20万/365日30万+ロール</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1664,7 @@
         </is>
       </c>
       <c r="C43" s="12" t="n">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="D43" s="12" t="n">
         <v>5</v>
@@ -1657,7 +1675,7 @@
       </c>
       <c r="F43" s="14" t="inlineStr">
         <is>
-          <t>ポイント制(女↑男↓)→蓄積換金・優遇↑</t>
+          <t>刻:5人5万/10人10万/+10万per10人/100人100万+ロール+Secret</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1702,7 @@
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>10Lvごとに逓増するマイルストーン</t>
+          <t>10Lvごと逓増マイルストーン</t>
         </is>
       </c>
     </row>
@@ -1696,11 +1714,11 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>ブースト達成</t>
+          <t>サバブ達成</t>
         </is>
       </c>
       <c r="C45" s="12" t="n">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="D45" s="12" t="n">
         <v>3</v>
@@ -1711,7 +1729,7 @@
       </c>
       <c r="F45" s="14" t="inlineStr">
         <is>
-          <t>支給額×月間達成件数</t>
+          <t>刻:3〜5万×回数(仮4万)</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1756,7 @@
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>会話必須VC限定→農耕無。提案↑50→100Gil/h×総在席h</t>
+          <t>刻:裁量で任せ→100Gil/h。会話VC限定</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1795,7 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>星導官 面接歩合</t>
+          <t>星導官 歩合(面接+個別)</t>
         </is>
       </c>
       <c r="C48" s="12" t="n">
@@ -1792,7 +1810,7 @@
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>完全歩合=星導官の全収入。3000×回数・○月上限120,000</t>
+          <t>完全歩合・全収入。面接3000×回＋個別対応1000×件・上限12万</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1853,7 @@
         </is>
       </c>
       <c r="C50" s="12" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="D50" s="12" t="n">
         <v>5</v>
@@ -1846,7 +1864,7 @@
       </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>仮上限=月50万(派手運用)。後で財務モデル見て調整</t>
+          <t>仮上限=月100万に増額(ステージ等のsink原資)</t>
         </is>
       </c>
     </row>
@@ -1913,14 +1931,14 @@
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>名前変更</t>
+          <t>名前変更(2回目以降)</t>
         </is>
       </c>
       <c r="C55" s="11" t="n">
-        <v>30000</v>
+        <v>100000</v>
       </c>
       <c r="D55" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E55" s="13">
         <f>C55*D55</f>
@@ -1928,7 +1946,7 @@
       </c>
       <c r="F55" s="14" t="inlineStr">
         <is>
-          <t>反復・既存</t>
+          <t>初回無料/2回目以降10万。ぽんぽん防止</t>
         </is>
       </c>
     </row>
@@ -1955,7 +1973,7 @@
       </c>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>追加・反復</t>
+          <t>反復</t>
         </is>
       </c>
     </row>
@@ -1982,7 +2000,7 @@
       </c>
       <c r="F57" s="14" t="inlineStr">
         <is>
-          <t>追加・反復</t>
+          <t>反復</t>
         </is>
       </c>
     </row>
@@ -2009,7 +2027,7 @@
       </c>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>追加・期間制</t>
+          <t>期間制</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2054,7 @@
       </c>
       <c r="F59" s="14" t="inlineStr">
         <is>
-          <t>サブスク継続課金・高額ゲート。数量=購読者数</t>
+          <t>月サブスク・格差ゲート。数量=購読者数</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2081,7 @@
       </c>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>サブスク継続課金。数量=購読者数</t>
+          <t>月サブスク。数量=購読者数</t>
         </is>
       </c>
     </row>
@@ -2075,14 +2093,14 @@
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>ステージ利用者証</t>
+          <t>18禁コンテンツロール</t>
         </is>
       </c>
       <c r="C61" s="11" t="n">
-        <v>50000</v>
+        <v>5000</v>
       </c>
       <c r="D61" s="12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E61" s="13">
         <f>C61*D61</f>
@@ -2090,19 +2108,19 @@
       </c>
       <c r="F61" s="14" t="inlineStr">
         <is>
-          <t>サブスク継続課金。数量=購読者数</t>
+          <t>刻案:普及狙いでサブスク5千/月(買切なら5万)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>高額</t>
+          <t>サブスク</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>18禁コンテンツロール</t>
+          <t>Sub垢 維持費</t>
         </is>
       </c>
       <c r="C62" s="11" t="n">
@@ -2117,7 +2135,7 @@
       </c>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>提案↓:80k→50k</t>
+          <t>刻決定:Sub垢の月維持費5万</t>
         </is>
       </c>
     </row>
@@ -2129,14 +2147,14 @@
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>黄金ネーム/名前飾り</t>
+          <t>ステージ利用者証</t>
         </is>
       </c>
       <c r="C63" s="11" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="D63" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E63" s="13">
         <f>C63*D63</f>
@@ -2144,7 +2162,7 @@
       </c>
       <c r="F63" s="14" t="inlineStr">
         <is>
-          <t>追加(A/E/F景品連動)</t>
+          <t>刻:最低30万。大型sink→イベント上限の原資</t>
         </is>
       </c>
     </row>
@@ -2156,11 +2174,11 @@
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>Sub垢導入</t>
+          <t>Sub垢 導入</t>
         </is>
       </c>
       <c r="C64" s="11" t="n">
-        <v>150000</v>
+        <v>300000</v>
       </c>
       <c r="D64" s="12" t="n">
         <v>2</v>
@@ -2171,7 +2189,7 @@
       </c>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>提案150k</t>
+          <t>刻決定:導入30万(維持費は別行)</t>
         </is>
       </c>
     </row>
@@ -2183,11 +2201,11 @@
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>限定カスタムロール</t>
+          <t>シクレ宿(価格仮)</t>
         </is>
       </c>
       <c r="C65" s="11" t="n">
-        <v>2000000</v>
+        <v>50000</v>
       </c>
       <c r="D65" s="12" t="n">
         <v>2</v>
@@ -2198,26 +2216,26 @@
       </c>
       <c r="F65" s="14" t="inlineStr">
         <is>
-          <t>提案2,000,000=鯨シンク。役職持ちが購入→販売数非ゼロ</t>
+          <t>要・刻確認(中身次第)。仮5万/回</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>部屋代金</t>
+          <t>鯨</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>宿代(2人個室VC・立て時)</t>
+          <t>限定カスタムロール</t>
         </is>
       </c>
       <c r="C66" s="11" t="n">
-        <v>8000</v>
+        <v>2000000</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E66" s="13">
         <f>C66*D66</f>
@@ -2225,7 +2243,7 @@
       </c>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>提案↑5k→8k(派手運用)。GILL実装済</t>
+          <t>刻:非グラデ前提で〇。グラデ可なら上位価格</t>
         </is>
       </c>
     </row>
@@ -2237,14 +2255,14 @@
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>ゲーム部屋 立て代金</t>
+          <t>宿代(2人個室)</t>
         </is>
       </c>
       <c r="C67" s="11" t="n">
         <v>8000</v>
       </c>
       <c r="D67" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E67" s="13">
         <f>C67*D67</f>
@@ -2252,328 +2270,382 @@
       </c>
       <c r="F67" s="14" t="inlineStr">
         <is>
-          <t>GILL実装済/価格未定。従量シンク</t>
+          <t>刻:問題無し</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="B68" s="15" t="inlineStr">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>部屋代金</t>
+        </is>
+      </c>
+      <c r="B68" s="10" t="inlineStr">
+        <is>
+          <t>ゲーム部屋(GO後)</t>
+        </is>
+      </c>
+      <c r="C68" s="11" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D68" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="E68" s="13">
+        <f>C68*D68</f>
+        <v/>
+      </c>
+      <c r="F68" s="14" t="inlineStr">
+        <is>
+          <t>刻:プレオープン無料/GO後8千</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>部屋代金</t>
+        </is>
+      </c>
+      <c r="B69" s="10" t="inlineStr">
+        <is>
+          <t>ゲーム部屋サブスク</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D69" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E69" s="13">
+        <f>C69*D69</f>
+        <v/>
+      </c>
+      <c r="F69" s="14" t="inlineStr">
+        <is>
+          <t>刻案:ヘビーユーザー向け立て放題</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="15" t="inlineStr">
         <is>
           <t>小計（Gilシンク_ショップ）</t>
         </is>
       </c>
-      <c r="E68" s="16">
-        <f>SUM(E55:E67)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="7" t="inlineStr">
+      <c r="E70" s="16">
+        <f>SUM(E55:E69)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="inlineStr">
         <is>
           <t>為替レバー（二通貨を繋ぐパイプ）</t>
         </is>
       </c>
-      <c r="B70" s="8" t="n"/>
-      <c r="C70" s="8" t="n"/>
-      <c r="D70" s="8" t="n"/>
-      <c r="E70" s="8" t="n"/>
-      <c r="F70" s="8" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="15" t="inlineStr">
+      <c r="B72" s="8" t="n"/>
+      <c r="C72" s="8" t="n"/>
+      <c r="D72" s="8" t="n"/>
+      <c r="E72" s="8" t="n"/>
+      <c r="F72" s="8" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="15" t="inlineStr">
         <is>
           <t>レバー</t>
         </is>
       </c>
-      <c r="B71" s="15" t="inlineStr">
+      <c r="B73" s="15" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="C71" s="15" t="inlineStr">
+      <c r="C73" s="15" t="inlineStr">
         <is>
           <t>値</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>為替レート R（1エテル=何Gil）</t>
-        </is>
-      </c>
-      <c r="C72" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="F72" s="18" t="inlineStr">
-        <is>
-          <t>我々が決定。Gil÷エテルの交換比</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>還光率 h（エテル→Gil 出口の目減り）</t>
-        </is>
-      </c>
-      <c r="C73" s="19" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F73" s="18" t="inlineStr">
-        <is>
-          <t>現状20%。半分JP/半分救済</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Gil→エテル 両替量 / 月（Gil）</t>
-        </is>
-      </c>
-      <c r="C74" s="20" t="n">
-        <v>0</v>
+          <t>為替レート R（1エテル=何Gil）</t>
+        </is>
+      </c>
+      <c r="C74" s="17" t="n">
+        <v>10</v>
       </c>
       <c r="F74" s="18" t="inlineStr">
         <is>
-          <t>接続後に実績。Gilは消滅</t>
+          <t>我々が決定。Gil÷エテルの交換比</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="B75" s="2" t="inlineStr">
         <is>
+          <t>還光率 h（エテル→Gil 出口の目減り）</t>
+        </is>
+      </c>
+      <c r="C75" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F75" s="18" t="inlineStr">
+        <is>
+          <t>現状20%。半分JP/半分救済</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Gil→エテル 両替量 / 月（Gil）</t>
+        </is>
+      </c>
+      <c r="C76" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="18" t="inlineStr">
+        <is>
+          <t>接続後に実績。Gilは消滅</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>エテル→Gil 換金量 / 月（エテル）</t>
         </is>
       </c>
-      <c r="C75" s="20" t="n">
+      <c r="C77" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="F75" s="18" t="inlineStr">
+      <c r="F77" s="18" t="inlineStr">
         <is>
           <t>接続後に実績</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="7" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
         <is>
           <t>カジノ行動前提（エテル経済の駆動・launch後データ待ち＝仮値）</t>
         </is>
       </c>
-      <c r="B77" s="8" t="n"/>
-      <c r="C77" s="8" t="n"/>
-      <c r="D77" s="8" t="n"/>
-      <c r="E77" s="8" t="n"/>
-      <c r="F77" s="8" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="15" t="inlineStr">
+      <c r="B79" s="8" t="n"/>
+      <c r="C79" s="8" t="n"/>
+      <c r="D79" s="8" t="n"/>
+      <c r="E79" s="8" t="n"/>
+      <c r="F79" s="8" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="15" t="inlineStr">
         <is>
           <t>前提</t>
         </is>
       </c>
-      <c r="B78" s="15" t="inlineStr">
+      <c r="B80" s="15" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="C78" s="15" t="inlineStr">
+      <c r="C80" s="15" t="inlineStr">
         <is>
           <t>値</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>アクティブ人数</t>
-        </is>
-      </c>
-      <c r="C79" s="21" t="n">
-        <v>30</v>
-      </c>
-      <c r="F79" s="18" t="inlineStr">
-        <is>
-          <t>エテルを動かす人数(仮)</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>1人あたり 月間プレイ回数</t>
-        </is>
-      </c>
-      <c r="C80" s="21" t="n">
-        <v>200</v>
-      </c>
-      <c r="F80" s="18" t="inlineStr">
-        <is>
-          <t>仮</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>平均ベット額（エテル）</t>
-        </is>
-      </c>
-      <c r="C81" s="17" t="n">
-        <v>500</v>
+          <t>アクティブ人数</t>
+        </is>
+      </c>
+      <c r="C81" s="21" t="n">
+        <v>30</v>
       </c>
       <c r="F81" s="18" t="inlineStr">
         <is>
-          <t>仮</t>
+          <t>エテルを動かす人数(仮)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>実効ハウスエッジ</t>
-        </is>
-      </c>
-      <c r="C82" s="19" t="n">
-        <v>0.05</v>
+          <t>1人あたり 月間プレイ回数</t>
+        </is>
+      </c>
+      <c r="C82" s="21" t="n">
+        <v>200</v>
       </c>
       <c r="F82" s="18" t="inlineStr">
         <is>
-          <t>4〜5%±2%。economy.ts</t>
+          <t>仮</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>福分け 1人1日 平均（エテル）</t>
+          <t>平均ベット額（エテル）</t>
         </is>
       </c>
       <c r="C83" s="17" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F83" s="18" t="inlineStr">
         <is>
-          <t>300/225/150/100の加重(仮)</t>
+          <t>仮</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="B84" s="2" t="inlineStr">
         <is>
+          <t>実効ハウスエッジ</t>
+        </is>
+      </c>
+      <c r="C84" s="19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F84" s="18" t="inlineStr">
+        <is>
+          <t>4〜5%±2%。economy.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>福分け 1人1日 平均（エテル）</t>
+        </is>
+      </c>
+      <c r="C85" s="17" t="n">
+        <v>200</v>
+      </c>
+      <c r="F85" s="18" t="inlineStr">
+        <is>
+          <t>300/225/150/100の加重(仮)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>月日数</t>
         </is>
       </c>
-      <c r="C84" s="21" t="n">
+      <c r="C86" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="F84" s="18" t="inlineStr">
+      <c r="F86" s="18" t="inlineStr">
         <is>
           <t>月→日換算</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="7" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="7" t="inlineStr">
         <is>
           <t>カジノ内パラメータ（参考・ハウス吸収の行先など）</t>
         </is>
       </c>
-      <c r="B86" s="8" t="n"/>
-      <c r="C86" s="8" t="n"/>
-      <c r="D86" s="8" t="n"/>
-      <c r="E86" s="8" t="n"/>
-      <c r="F86" s="8" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="15" t="inlineStr">
+      <c r="B88" s="8" t="n"/>
+      <c r="C88" s="8" t="n"/>
+      <c r="D88" s="8" t="n"/>
+      <c r="E88" s="8" t="n"/>
+      <c r="F88" s="8" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="15" t="inlineStr">
         <is>
           <t>参考</t>
         </is>
       </c>
-      <c r="B87" s="15" t="inlineStr">
+      <c r="B89" s="15" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="C87" s="15" t="inlineStr">
+      <c r="C89" s="15" t="inlineStr">
         <is>
           <t>値</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>ハウス吸収→消滅 率</t>
-        </is>
-      </c>
-      <c r="C88" s="19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F88" s="18" t="inlineStr">
-        <is>
-          <t>economy.distributeHouseEarnings</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>ハウス吸収→救済 率</t>
-        </is>
-      </c>
-      <c r="C89" s="19" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F89" s="18" t="inlineStr">
-        <is>
-          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>ハウス吸収→JP 率</t>
+          <t>ハウス吸収→消滅 率</t>
         </is>
       </c>
       <c r="C90" s="19" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="F90" s="18" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>economy.distributeHouseEarnings</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>初期残高（エテル）</t>
-        </is>
-      </c>
-      <c r="C91" s="17" t="n">
-        <v>3000</v>
+          <t>ハウス吸収→救済 率</t>
+        </is>
+      </c>
+      <c r="C91" s="19" t="n">
+        <v>0.3</v>
       </c>
       <c r="F91" s="18" t="inlineStr">
         <is>
-          <t>db.ts</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="B92" s="2" t="inlineStr">
         <is>
+          <t>ハウス吸収→JP 率</t>
+        </is>
+      </c>
+      <c r="C92" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F92" s="18" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>初期残高（エテル）</t>
+        </is>
+      </c>
+      <c r="C93" s="17" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F93" s="18" t="inlineStr">
+        <is>
+          <t>db.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>残高上限（エテル）</t>
         </is>
       </c>
-      <c r="C92" s="17" t="n">
+      <c r="C94" s="17" t="n">
         <v>300000</v>
       </c>
-      <c r="F92" s="18" t="inlineStr">
+      <c r="F94" s="18" t="inlineStr">
         <is>
           <t>db.ts</t>
         </is>
@@ -2701,7 +2773,7 @@
         </is>
       </c>
       <c r="B11" s="22">
-        <f>SUM('前提・レバー'!$E$55:$E$67)</f>
+        <f>SUM('前提・レバー'!$E$55:$E$69)</f>
         <v/>
       </c>
       <c r="C11" s="18" t="inlineStr">
@@ -2717,7 +2789,7 @@
         </is>
       </c>
       <c r="B12" s="22">
-        <f>'前提・レバー'!$C$74</f>
+        <f>'前提・レバー'!$C$76</f>
         <v/>
       </c>
       <c r="C12" s="18" t="inlineStr">
@@ -2751,7 +2823,7 @@
         </is>
       </c>
       <c r="B16" s="22">
-        <f>'前提・レバー'!$C$75*(1-'前提・レバー'!$C$73)/'前提・レバー'!$C$72</f>
+        <f>'前提・レバー'!$C$77*(1-'前提・レバー'!$C$75)/'前提・レバー'!$C$74</f>
         <v/>
       </c>
       <c r="C16" s="18" t="inlineStr">
@@ -2855,7 +2927,7 @@
         </is>
       </c>
       <c r="B4" s="22">
-        <f>'前提・レバー'!$C$79*'前提・レバー'!$C$80*'前提・レバー'!$C$81</f>
+        <f>'前提・レバー'!$C$81*'前提・レバー'!$C$82*'前提・レバー'!$C$83</f>
         <v/>
       </c>
       <c r="C4" s="18" t="inlineStr">
@@ -2871,7 +2943,7 @@
         </is>
       </c>
       <c r="B5" s="22">
-        <f>B4*'前提・レバー'!$C$82</f>
+        <f>B4*'前提・レバー'!$C$84</f>
         <v/>
       </c>
       <c r="C5" s="18" t="inlineStr">
@@ -2887,7 +2959,7 @@
         </is>
       </c>
       <c r="B6" s="22">
-        <f>'前提・レバー'!$C$79*'前提・レバー'!$C$83*'前提・レバー'!$C$84</f>
+        <f>'前提・レバー'!$C$81*'前提・レバー'!$C$85*'前提・レバー'!$C$86</f>
         <v/>
       </c>
       <c r="C6" s="18" t="inlineStr">
@@ -2921,7 +2993,7 @@
         </is>
       </c>
       <c r="B10" s="22">
-        <f>'前提・レバー'!$C$74/'前提・レバー'!$C$72</f>
+        <f>'前提・レバー'!$C$76/'前提・レバー'!$C$74</f>
         <v/>
       </c>
       <c r="C10" s="18" t="inlineStr">
@@ -2955,7 +3027,7 @@
         </is>
       </c>
       <c r="B14" s="22">
-        <f>B5*'前提・レバー'!$C$88</f>
+        <f>B5*'前提・レバー'!$C$90</f>
         <v/>
       </c>
       <c r="C14" s="18" t="inlineStr">
@@ -2971,7 +3043,7 @@
         </is>
       </c>
       <c r="B15" s="22">
-        <f>'前提・レバー'!$C$75*(1-'前提・レバー'!$C$73)</f>
+        <f>'前提・レバー'!$C$77*(1-'前提・レバー'!$C$75)</f>
         <v/>
       </c>
       <c r="C15" s="18" t="inlineStr">
@@ -3026,7 +3098,7 @@
         </is>
       </c>
       <c r="B20" s="22">
-        <f>B5*('前提・レバー'!$C$89+'前提・レバー'!$C$90)</f>
+        <f>B5*('前提・レバー'!$C$91+'前提・レバー'!$C$92)</f>
         <v/>
       </c>
       <c r="C20" s="18" t="inlineStr">
@@ -3457,7 +3529,7 @@
         </is>
       </c>
       <c r="B10" s="32">
-        <f>'前提・レバー'!$C$72</f>
+        <f>'前提・レバー'!$C$74</f>
         <v/>
       </c>
       <c r="C10" s="14" t="inlineStr">
@@ -3473,7 +3545,7 @@
         </is>
       </c>
       <c r="B11" s="33">
-        <f>'前提・レバー'!$C$73</f>
+        <f>'前提・レバー'!$C$75</f>
         <v/>
       </c>
       <c r="C11" s="14" t="inlineStr">
@@ -3528,7 +3600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4008,71 +4080,131 @@
         <v/>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="36">
+        <f>'前提・レバー'!$B$68</f>
+        <v/>
+      </c>
+      <c r="B19" s="32">
+        <f>'前提・レバー'!$C$68</f>
+        <v/>
+      </c>
+      <c r="C19" s="37">
+        <f>IF(C$5=0,0,$B19/C$5)</f>
+        <v/>
+      </c>
+      <c r="D19" s="37">
+        <f>IF(D$5=0,0,$B19/D$5)</f>
+        <v/>
+      </c>
+      <c r="E19" s="37">
+        <f>IF(E$5=0,0,$B19/E$5)</f>
+        <v/>
+      </c>
+      <c r="F19" s="37">
+        <f>IF(F$5=0,0,$B19/F$5)</f>
+        <v/>
+      </c>
+      <c r="G19" s="37">
+        <f>IF(G$5=0,0,$B19/G$5)</f>
+        <v/>
+      </c>
+    </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="36">
+        <f>'前提・レバー'!$B$69</f>
+        <v/>
+      </c>
+      <c r="B20" s="32">
+        <f>'前提・レバー'!$C$69</f>
+        <v/>
+      </c>
+      <c r="C20" s="37">
+        <f>IF(C$5=0,0,$B20/C$5)</f>
+        <v/>
+      </c>
+      <c r="D20" s="37">
+        <f>IF(D$5=0,0,$B20/D$5)</f>
+        <v/>
+      </c>
+      <c r="E20" s="37">
+        <f>IF(E$5=0,0,$B20/E$5)</f>
+        <v/>
+      </c>
+      <c r="F20" s="37">
+        <f>IF(F$5=0,0,$B20/F$5)</f>
+        <v/>
+      </c>
+      <c r="G20" s="37">
+        <f>IF(G$5=0,0,$B20/G$5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>■ 目標バンドの目安（主層基準）</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="18" t="inlineStr">
-        <is>
-          <t>・消耗品（反復）: 〜1ヶ月  … 気軽に何度も買える</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="18" t="inlineStr">
-        <is>
-          <t>・通行証・中位: 1〜3ヶ月  … 貯めれば手が届く</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="18" t="inlineStr">
         <is>
-          <t>・中ステータス: 3〜6ヶ月  … 目標になる</t>
+          <t>・消耗品（反復）: 〜1ヶ月  … 気軽に何度も買える</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="18" t="inlineStr">
         <is>
-          <t>・最上位ステータス: 6〜12ヶ月  … 憧れ・長期目標</t>
+          <t>・通行証・中位: 1〜3ヶ月  … 貯めれば手が届く</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="18" t="inlineStr">
         <is>
-          <t>・12ヶ月超: 原則 価格↓ or 給与↑ を検討</t>
+          <t>・中ステータス: 3〜6ヶ月  … 目標になる</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="18" t="inlineStr">
         <is>
-          <t>・※例外=鯨の蓄財シンク（限定カスタムロール等）: 意図的にバンド外。カジノ大勝ち/蓄財/イベント報酬を吸う最上位プレステージ。主層の取得時間で測らない</t>
+          <t>・最上位ステータス: 6〜12ヶ月  … 憧れ・長期目標</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="18" t="inlineStr">
         <is>
-          <t>・※サブスク=通行証（継続課金）: 表の値は『月収の何倍/期の維持費』と読む。&gt;1=収入だけでは維持不可＝富裕層向けの格差ゲート（意図的）</t>
+          <t>・12ヶ月超: 原則 価格↓ or 給与↑ を検討</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="18" t="inlineStr">
         <is>
+          <t>・※例外=鯨の蓄財シンク（限定カスタムロール等）: 意図的にバンド外。カジノ大勝ち/蓄財/イベント報酬を吸う最上位プレステージ。主層の取得時間で測らない</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>・※サブスク=通行証（継続課金）: 表の値は『月収の何倍/期の維持費』と読む。&gt;1=収入だけでは維持不可＝富裕層向けの格差ゲート（意図的）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
           <t>・設計原則: 格差はそこそこ許容（給与スプレッド維持・高額財は高く・過度な平準化はしない）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C6:G18">
+  <conditionalFormatting sqref="C6:G20">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4362,4 +4494,461 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>定員プラン — 各役職を何人雇えるか（予算 vs シンク）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>青字=入力。役職の定員を変えると残予算が動く。月給/歩合/身分給は前提シートと連動。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>給与予算 / 月（シンク連動）</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>堅い1.3M〜現状2.5M〜カジノ後4M</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>− 身分給（会員数で決まる固定費）</t>
+        </is>
+      </c>
+      <c r="B5" s="22">
+        <f>'前提・レバー'!E10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>＝ 役職に回せる予算</t>
+        </is>
+      </c>
+      <c r="B6" s="16">
+        <f>B4-B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>役職</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>月給/人</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>定員(計画)</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>月額</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>モーセの十戒</t>
+        </is>
+      </c>
+      <c r="B9" s="32">
+        <f>'前提・レバー'!C14</f>
+        <v/>
+      </c>
+      <c r="C9" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="13">
+        <f>B9*C9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>天銀官</t>
+        </is>
+      </c>
+      <c r="B10" s="32">
+        <f>'前提・レバー'!C15</f>
+        <v/>
+      </c>
+      <c r="C10" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="13">
+        <f>B10*C10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>星導官</t>
+        </is>
+      </c>
+      <c r="B11" s="32">
+        <f>'前提・レバー'!C16</f>
+        <v/>
+      </c>
+      <c r="C11" s="39" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" s="13">
+        <f>B11*C11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>審星官・特級</t>
+        </is>
+      </c>
+      <c r="B12" s="32">
+        <f>'前提・レバー'!C17</f>
+        <v/>
+      </c>
+      <c r="C12" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="13">
+        <f>B12*C12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>審星官・Ⅰ級</t>
+        </is>
+      </c>
+      <c r="B13" s="32">
+        <f>'前提・レバー'!C18</f>
+        <v/>
+      </c>
+      <c r="C13" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="13">
+        <f>B13*C13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>審星官・Ⅱ級</t>
+        </is>
+      </c>
+      <c r="B14" s="32">
+        <f>'前提・レバー'!C19</f>
+        <v/>
+      </c>
+      <c r="C14" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="13">
+        <f>B14*C14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>審星官・Ⅲ級</t>
+        </is>
+      </c>
+      <c r="B15" s="32">
+        <f>'前提・レバー'!C20</f>
+        <v/>
+      </c>
+      <c r="C15" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="13">
+        <f>B15*C15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>審星官・見習い</t>
+        </is>
+      </c>
+      <c r="B16" s="32">
+        <f>'前提・レバー'!C21</f>
+        <v/>
+      </c>
+      <c r="C16" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" s="13">
+        <f>B16*C16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>星祭官</t>
+        </is>
+      </c>
+      <c r="B17" s="32">
+        <f>'前提・レバー'!C22</f>
+        <v/>
+      </c>
+      <c r="C17" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="13">
+        <f>B17*C17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>印章官</t>
+        </is>
+      </c>
+      <c r="B18" s="32">
+        <f>'前提・レバー'!C23</f>
+        <v/>
+      </c>
+      <c r="C18" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="13">
+        <f>B18*C18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>星商官</t>
+        </is>
+      </c>
+      <c r="B19" s="32">
+        <f>'前提・レバー'!C24</f>
+        <v/>
+      </c>
+      <c r="C19" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="13">
+        <f>B19*C19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>幻戯官</t>
+        </is>
+      </c>
+      <c r="B20" s="32">
+        <f>'前提・レバー'!C25</f>
+        <v/>
+      </c>
+      <c r="C20" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="13">
+        <f>B20*C20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>失星官</t>
+        </is>
+      </c>
+      <c r="B21" s="32">
+        <f>'前提・レバー'!C26</f>
+        <v/>
+      </c>
+      <c r="C21" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="13">
+        <f>B21*C21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>贖罪官</t>
+        </is>
+      </c>
+      <c r="B22" s="32">
+        <f>'前提・レバー'!C27</f>
+        <v/>
+      </c>
+      <c r="C22" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="13">
+        <f>B22*C22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>星賭官</t>
+        </is>
+      </c>
+      <c r="B23" s="32">
+        <f>'前提・レバー'!C28</f>
+        <v/>
+      </c>
+      <c r="C23" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="13">
+        <f>B23*C23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>18禁</t>
+        </is>
+      </c>
+      <c r="B24" s="32">
+        <f>'前提・レバー'!C29</f>
+        <v/>
+      </c>
+      <c r="C24" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="13">
+        <f>B24*C24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>※星導官=完全歩合(基本給0)。定員を増やしても固定費0・働いた分のみ上限12万/人</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>役職コスト 計</t>
+        </is>
+      </c>
+      <c r="D26" s="26">
+        <f>SUM(D9:D24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>＋歩合（評価+星導+星賭）</t>
+        </is>
+      </c>
+      <c r="D27" s="22">
+        <f>'前提・レバー'!E47+'前提・レバー'!E48+'前提・レバー'!E49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>残予算（役職予算−コスト−歩合）</t>
+        </is>
+      </c>
+      <c r="D28" s="26">
+        <f>B6-D26-D27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>■ 読み方</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t>・身分給(会員数)が先に予算を食う → 役職は“その残り”で雇う</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="inlineStr">
+        <is>
+          <t>・残予算マイナス＝シンク不足。カジノ接続 or サブスク増 or 会員増で枠が開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="18" t="inlineStr">
+        <is>
+          <t>・星導官は完全歩合＝定員を増やしても固定費は増えない（働いた分のみ）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D28">
+    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>